--- a/artfynd/A 62416-2025 artfynd.xlsx
+++ b/artfynd/A 62416-2025 artfynd.xlsx
@@ -887,7 +887,7 @@
         <v>130191655</v>
       </c>
       <c r="B4" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 62416-2025 artfynd.xlsx
+++ b/artfynd/A 62416-2025 artfynd.xlsx
@@ -887,7 +887,7 @@
         <v>130191655</v>
       </c>
       <c r="B4" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 62416-2025 artfynd.xlsx
+++ b/artfynd/A 62416-2025 artfynd.xlsx
@@ -887,7 +887,7 @@
         <v>130191655</v>
       </c>
       <c r="B4" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 62416-2025 artfynd.xlsx
+++ b/artfynd/A 62416-2025 artfynd.xlsx
@@ -887,7 +887,7 @@
         <v>130191655</v>
       </c>
       <c r="B4" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 62416-2025 artfynd.xlsx
+++ b/artfynd/A 62416-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,45 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129797333</v>
+        <v>130191655</v>
       </c>
       <c r="B2" t="n">
-        <v>57738</v>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Halvfaritberget, Vb</t>
+          <t>Umeå-Örnsköldsvik, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>743219</v>
+        <v>743319</v>
       </c>
       <c r="R2" t="n">
-        <v>7092841</v>
+        <v>7092695</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -740,12 +740,27 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>NVI (C250260) Calluna AB</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -760,44 +775,44 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Jonas Mattsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Elin Kannerby</t>
+          <t>Anna Koffman</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130191654</v>
+        <v>130191658</v>
       </c>
       <c r="B3" t="n">
-        <v>5197</v>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>105930</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>743317</v>
+        <v>743385</v>
       </c>
       <c r="R3" t="n">
-        <v>7092692</v>
+        <v>7092830</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -842,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -852,7 +867,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -884,14 +899,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130191655</v>
+        <v>130191659</v>
       </c>
       <c r="B4" t="n">
-        <v>79211</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -919,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>743319</v>
+        <v>743386</v>
       </c>
       <c r="R4" t="n">
-        <v>7092695</v>
+        <v>7092832</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,6 +1008,215 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>129797333</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Halvfaritberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>743219</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7092841</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Elin Kannerby</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>130191654</v>
+      </c>
+      <c r="B6" t="n">
+        <v>5199</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Umeå-Örnsköldsvik, Vb</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>743317</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7092692</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Vännäs</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>NVI (C250260) Calluna AB</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Jonas Mattsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Anna Koffman</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 62416-2025 artfynd.xlsx
+++ b/artfynd/A 62416-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -784,6 +789,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130191655</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -896,6 +906,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130191658</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1008,6 +1023,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130191659</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1105,6 +1125,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129797333</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1217,8 +1242,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130191654</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>